--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/demo/data_retention_demo.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/demo/data_retention_demo.xlsx
@@ -84,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -98,11 +98,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +159,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -615,7 +645,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Art. 6 — Lawful basis: consent, contract, legal obligation, legitimate interest</t>
+          <t>Art. 6 — Six lawful bases: consent, contract, legal obligation, vital interests, public task, legitimate interest</t>
         </is>
       </c>
     </row>
@@ -811,164 +841,56 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Art. 6(1)(c) - Legal Obligation"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Art. 6(1)(c) - Legal Obligation"
 Reasoning: Legal obligation because adverse event reporting is mandated by law</t>
-          </r>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"25 years (per ICH-GCP)"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"25 years (per ICH-GCP)"
 Reasoning: ICH-GCP requires 25-year retention for safety data — longest retention period</t>
-          </r>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Pharmacovigilance database with audit trail"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Pharmacovigilance database with audit trail"
 Reasoning: Pharmacovigilance DB needs full audit trail for regulatory inspections</t>
-          </r>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Safety team + regulatory access only"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Safety team + regulatory access only"
 Reasoning: Highly restricted — only safety and regulatory teams should access</t>
-          </r>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Yes"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Yes"
 Reasoning: Sensitive patient safety data requires encryption</t>
-          </r>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Archival after retention; cryptographic erasure"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Archival after retention; cryptographic erasure"
 Reasoning: Cannot delete safety data early; archival after mandatory period</t>
-          </r>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Mandatory retention per EMA/FDA guidelines; no early deletion"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Mandatory retention per EMA/FDA guidelines; no early deletion"
 Reasoning: No exceptions — regulatory requirement overrides deletion requests</t>
-          </r>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Head of Pharmacovigilance"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Head of Pharmacovigilance"
 Reasoning: Pharmacovigilance head owns safety data by regulation</t>
-          </r>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"2026-02-01"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"2026-02-01"
 Reasoning: Annual review cycle</t>
-          </r>
         </is>
       </c>
     </row>
@@ -990,164 +912,56 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Art. 6(1)(f) - Legitimate Interest"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Art. 6(1)(f) - Legitimate Interest"
 Reasoning: Legitimate interest for model training, balanced against data subject rights</t>
-          </r>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"3 years after model retirement"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"3 years after model retirement"
 Reasoning: 3 years post-retirement allows for audit and reproducibility verification</t>
-          </r>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Encrypted data lake (S3)"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Encrypted data lake (S3)"
 Reasoning: Cloud storage with encryption for large ML datasets</t>
-          </r>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"ML team only, IP-restricted"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"ML team only, IP-restricted"
 Reasoning: Only ML team accesses training data; IP restriction adds network-level control</t>
-          </r>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Yes"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Yes"
 Reasoning: Training data for sensitive models requires encryption</t>
-          </r>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Cryptographic erasure"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Cryptographic erasure"
 Reasoning: Cryptographic erasure is gold standard for cloud storage deletion</t>
-          </r>
         </is>
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Retain for model audit/reproducibility"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Retain for model audit/reproducibility"
 Reasoning: Must keep for regulatory audit of model decisions</t>
-          </r>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"ML Engineering Manager"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"ML Engineering Manager"
 Reasoning: ML team owns training data assets</t>
-          </r>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"2026-02-01"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"2026-02-01"
 Reasoning: Annual review cycle</t>
-          </r>
         </is>
       </c>
     </row>
@@ -1169,164 +983,56 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Art. 6(1)(c) - Legal Obligation"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Art. 6(1)(c) - Legal Obligation"
 Reasoning: Legal obligation to maintain audit trail for regulatory compliance</t>
-          </r>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"7 years"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"7 years"
 Reasoning: 7-year standard for compliance records across FDA and GDPR</t>
-          </r>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Immutable log storage (WORM)"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Immutable log storage (WORM)"
 Reasoning: WORM (Write Once Read Many) ensures immutability for regulatory proof</t>
-          </r>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Compliance team only"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Compliance team only"
 Reasoning: Audit logs restricted to compliance to prevent tampering</t>
-          </r>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Yes"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Yes"
 Reasoning: Audit logs contain sensitive access information</t>
-          </r>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Automatic purge after retention period"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Automatic purge after retention period"
 Reasoning: Automated purge after 7 years to minimize data footprint</t>
-          </r>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Required by regulation; cannot be shortened"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Required by regulation; cannot be shortened"
 Reasoning: Regulatory requirement — no exceptions allowed</t>
-          </r>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Chief Data Officer"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Chief Data Officer"
 Reasoning: CDO ensures compliance across all data categories</t>
-          </r>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"2026-02-01"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"2026-02-01"
 Reasoning: Annual review cycle</t>
-          </r>
         </is>
       </c>
     </row>
@@ -1336,6 +1042,17 @@
           <t>TIP: Consider the interplay between GDPR's 'storage limitation' principle and industry-specific retention mandates (e.g., FDA requires 25 years for safety data even though GDPR favors minimal retention).</t>
         </is>
       </c>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1452,128 +1169,44 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Data Inventory &amp; Impact Assessment"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Data Inventory &amp; Impact Assessment"
 Reasoning: Second step combines inventory and impact assessment to efficiently identify scope</t>
-          </r>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Identify all systems storing participant's data; assess AI model dependencies"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Identify all systems storing participant's data; assess AI model dependencies"
 Reasoning: Need both data AND model dependencies to understand full deletion impact</t>
-          </r>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"ML Engineering Manager + Data Governance"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"ML Engineering Manager + Data Governance"
 Reasoning: Joint ML + governance because deletion affects both data stores and models</t>
-          </r>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"48 hours"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"48 hours"
 Reasoning: 48 hours accounts for complex data landscape across multiple systems</t>
-          </r>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Cross-reference all databases, training datasets, and model lineage"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Cross-reference all databases, training datasets, and model lineage"
 Reasoning: Must check training data, not just operational data</t>
-          </r>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"CDO if model retraining needed"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"CDO if model retraining needed"
 Reasoning: CDO escalation when models are affected ensures business-level decision making</t>
-          </r>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Data inventory report + model impact assessment"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Data inventory report + model impact assessment"
 Reasoning: Two artifacts capture both data scope and model impact</t>
-          </r>
         </is>
       </c>
     </row>
@@ -1583,128 +1216,44 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Deletion Execution &amp; Verification"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Deletion Execution &amp; Verification"
 Reasoning: Execution and verification paired because verification must immediately follow deletion</t>
-          </r>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Execute secure deletion across all identified systems; verify no recovery paths"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Execute secure deletion across all identified systems; verify no recovery paths"
 Reasoning: Must cover ALL systems including backups — pharma companies have extensive backup chains</t>
-          </r>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Database Administrator + Security"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Database Administrator + Security"
 Reasoning: DBA executes, security verifies — separation of duties for audit compliance</t>
-          </r>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"5 days"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"5 days"
 Reasoning: 5 days because pharma has many storage tiers (primary, backup, archive, disaster recovery)</t>
-          </r>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Checksum verification, backup scan, recovery test"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Checksum verification, backup scan, recovery test"
 Reasoning: Three-layer verification: checksum, backup scan, and recovery test</t>
-          </r>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"CTO if deletion incomplete"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"CTO if deletion incomplete"
 Reasoning: CTO escalation if deletion can't be completed ensures top-level accountability</t>
-          </r>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Deletion execution log with timestamps and verification certificates"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Deletion execution log with timestamps and verification certificates"
 Reasoning: Timestamps and certificates provide regulatory-grade evidence</t>
-          </r>
         </is>
       </c>
     </row>
@@ -1714,128 +1263,44 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Confirmation &amp; Audit Logging"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Confirmation &amp; Audit Logging"
 Reasoning: Final step closes the loop with both the participant and the audit trail</t>
-          </r>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Notify participant of completion; create immutable audit record"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Notify participant of completion; create immutable audit record"
 Reasoning: GDPR requires notification to the data subject</t>
-          </r>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Privacy Officer + Compliance"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Privacy Officer + Compliance"
 Reasoning: Privacy handles notification, compliance handles audit record</t>
-          </r>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"3 days"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"3 days"
 Reasoning: 3 days allows for thorough documentation and certified mail</t>
-          </r>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Confirm no residual data; validate audit completeness"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Confirm no residual data; validate audit completeness"
 Reasoning: Final verification that nothing was missed</t>
-          </r>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Regulatory Affairs if regulatory reporting needed"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Regulatory Affairs if regulatory reporting needed"
 Reasoning: Regulatory Affairs if threshold for Data Protection Authority notification is met</t>
-          </r>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Confirmation letter + signed audit log entry"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Confirmation letter + signed audit log entry"
 Reasoning: Two outputs: external confirmation and internal audit record</t>
-          </r>
         </is>
       </c>
     </row>
@@ -1845,6 +1310,13 @@
           <t>TIP: In pharma, deletion workflows must account for regulatory holds — some data cannot be deleted even upon request if it relates to ongoing safety monitoring.</t>
         </is>
       </c>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1970,110 +1442,38 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Adverse Event Detector v3.2, Signal Detection Model v1.5"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Adverse Event Detector v3.2, Signal Detection Model v1.5"
 Reasoning: Both safety models depend on adverse event data</t>
-          </r>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"High"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"High"
 Reasoning: High because adverse event data is the core training input for safety models</t>
-          </r>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Yes"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Yes"
 Reasoning: Cannot operate safety models on degraded training data</t>
-          </r>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"14-21 days"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"14-21 days"
 Reasoning: 14-21 days accounts for retraining + validation + regulatory review</t>
-          </r>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"VP of R&amp;D + Regulatory Affairs"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"VP of R&amp;D + Regulatory Affairs"
 Reasoning: VP R&amp;D and Regulatory because safety model changes have regulatory implications</t>
-          </r>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Core training data; deletion of safety reports directly impacts model accuracy and regulatory compliance"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Core training data; deletion of safety reports directly impacts model accuracy and regulatory compliance"
 Reasoning: Regulatory compliance makes this non-negotiable</t>
-          </r>
         </is>
       </c>
     </row>
@@ -2090,110 +1490,38 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Adverse Event Detector v3.2"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Adverse Event Detector v3.2"
 Reasoning: Primary model using this training data</t>
-          </r>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Critical"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Critical"
 Reasoning: Critical because this IS the training data — direct impact on model validity</t>
-          </r>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Yes (Priority)"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Yes (Priority)"
 Reasoning: Yes, priority — model may produce unreliable results</t>
-          </r>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Immediate reassessment, 7 days for retraining"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Immediate reassessment, 7 days for retraining"
 Reasoning: Immediate assessment with fast turnaround for patient safety</t>
-          </r>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Chief Data Officer"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Chief Data Officer"
 Reasoning: CDO for critical decisions affecting model reliability</t>
-          </r>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Direct deletion of training data; model accuracy may be immediately compromised; emergency retraining protocol activates"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Direct deletion of training data; model accuracy may be immediately compromised; emergency retraining protocol activates"
 Reasoning: Emergency protocol because model serves patient safety function</t>
-          </r>
         </is>
       </c>
     </row>
@@ -2203,6 +1531,13 @@
           <t>TIP: In healthcare/pharma, retraining safety-critical models requires re-validation and may need regulatory re-approval before redeployment.</t>
         </is>
       </c>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/11_compliance-mapping-for-ai-systems-gdpr-cpra/demo/data_retention_demo.xlsx
+++ b/11_compliance-mapping-for-ai-systems-gdpr-cpra/demo/data_retention_demo.xlsx
@@ -847,8 +847,8 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>"25 years (per ICH-GCP)"
-Reasoning: ICH-GCP requires 25-year retention for safety data — longest retention period</t>
+          <t>"25 years"
+Reasoning: EU CTR 536/2014 Art. 58 requires 25-year retention of the clinical trial master file; ICH-GCP E6(R3) defers to applicable regulatory requirements.</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
@@ -990,7 +990,7 @@
       <c r="E5" s="10" t="inlineStr">
         <is>
           <t>"7 years"
-Reasoning: 7-year standard for compliance records across FDA and GDPR</t>
+Reasoning: 7 years is an internal compliance-records standard; HIPAA's 6-year rule covers Security-Rule documentation and GDPR sets no fixed period.</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>TIP: Consider the interplay between GDPR's 'storage limitation' principle and industry-specific retention mandates (e.g., FDA requires 25 years for safety data even though GDPR favors minimal retention).</t>
+          <t>TIP: Consider the interplay between GDPR's 'storage limitation' principle and industry-specific retention mandates (e.g., EU CTR 536/2014 Art. 58 requires 25-year retention of the clinical trial master file even though GDPR favors minimal retention).</t>
         </is>
       </c>
       <c r="B6" s="12" t="n"/>
